--- a/excel/Appium_Mobile_E2E_Test_Report_300.xlsx
+++ b/excel/Appium_Mobile_E2E_Test_Report_300.xlsx
@@ -17,7 +17,7 @@
     <t>TURFINGTON MOBILE APP - APPIUM 2.X E2E TEST AUTOMATION SUMMARY</t>
   </si>
   <si>
-    <t>Mobile App Frontend (Android &amp; iOS) Capacitor Hybrid Automation • Generated on 10/31/2026, 1:03:59 AM GMT+5:30</t>
+    <t>Mobile App Frontend (Android &amp; iOS) Capacitor Hybrid Automation • Generated on 10/31/2026, 1:02:39 PM GMT+5:30</t>
   </si>
   <si>
     <t>TOTAL TEST CASES</t>
